--- a/data/trans_dic/P25C$otraforma_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P25C$otraforma_2023-Estudios-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo método para dejar de fumar fue otro</t>
+          <t>Población cuyo método para dejar de fumar fue otro (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,38; 7,82</t>
+          <t>1,35; 7,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,27</t>
+          <t>0,0; 6,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,22; 6,52</t>
+          <t>1,35; 6,49</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,49; 5,7</t>
+          <t>0,72; 5,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,06; 6,24</t>
+          <t>2,06; 6,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,1; 4,78</t>
+          <t>1,0; 4,98</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,85; 7,3</t>
+          <t>0,85; 7,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,93</t>
+          <t>0,0; 4,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,94; 5,09</t>
+          <t>0,9; 4,96</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,04; 4,69</t>
+          <t>1,14; 4,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,59; 4,61</t>
+          <t>1,68; 4,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,42; 4,09</t>
+          <t>1,44; 4,21</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo método para dejar de fumar fue otro</t>
+          <t>Población cuyo método para dejar de fumar fue otro (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2280; 12964</t>
+          <t>2234; 13031</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3223</t>
+          <t>0; 2962</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2556; 13689</t>
+          <t>2840; 13643</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2641; 31016</t>
+          <t>3931; 32021</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4190; 12683</t>
+          <t>4177; 13244</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8209; 35751</t>
+          <t>7509; 37252</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1174; 10025</t>
+          <t>1174; 10355</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4293</t>
+          <t>0; 4107</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2099; 11420</t>
+          <t>2030; 11127</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8820; 39779</t>
+          <t>9642; 40548</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5305; 15428</t>
+          <t>5627; 15565</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16803; 48372</t>
+          <t>17054; 49768</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P25C$otraforma_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P25C$otraforma_2023-Estudios-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,35; 7,86</t>
+          <t>1,55; 7,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,68</t>
+          <t>0,0; 7,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,35; 6,49</t>
+          <t>1,3; 5,85</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,72; 5,88</t>
+          <t>2,82; 7,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,06; 6,52</t>
+          <t>1,9; 6,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,0; 4,98</t>
+          <t>2,93; 6,33</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,85; 7,54</t>
+          <t>1,29; 7,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,72</t>
+          <t>0,0; 5,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,9; 4,96</t>
+          <t>1,21; 5,19</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,68%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,14; 4,78</t>
+          <t>2,83; 5,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,68; 4,65</t>
+          <t>1,61; 4,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,44; 4,21</t>
+          <t>2,66; 4,96</t>
         </is>
       </c>
     </row>
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6156</t>
+          <t>6310</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>670</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6768</t>
+          <t>6980</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2234; 13031</t>
+          <t>2738; 13409</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 2962</t>
+          <t>0; 3752</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2840; 13643</t>
+          <t>2896; 13055</t>
         </is>
       </c>
     </row>
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>14081</t>
+          <t>16192</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>7542</t>
+          <t>7823</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>21624</t>
+          <t>24015</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3931; 32021</t>
+          <t>9375; 26124</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4177; 13244</t>
+          <t>4229; 13705</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7509; 37252</t>
+          <t>16232; 35086</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4059</t>
+          <t>5203</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1313</t>
+          <t>1395</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5372</t>
+          <t>6597</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1174; 10355</t>
+          <t>1922; 11880</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4107</t>
+          <t>0; 4934</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2030; 11127</t>
+          <t>2945; 12679</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>24296</t>
+          <t>27705</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>9467</t>
+          <t>9888</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>33763</t>
+          <t>37593</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9642; 40548</t>
+          <t>18571; 39138</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5627; 15565</t>
+          <t>5868; 16818</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17054; 49768</t>
+          <t>27192; 50743</t>
         </is>
       </c>
     </row>
